--- a/data/trans_camb/P45C_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 12,99</t>
+          <t>2,31; 13,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,52</t>
+          <t>-5,0; 6,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 5,23</t>
+          <t>-9,99; 6,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 8,93</t>
+          <t>-2,7; 8,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 3,32</t>
+          <t>-8,84; 2,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 3,07</t>
+          <t>-12,39; 2,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,45</t>
+          <t>1,3; 9,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,39</t>
+          <t>-4,66; 3,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 2,02</t>
+          <t>-9,33; 1,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 61,06</t>
+          <t>8,4; 63,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 32,05</t>
+          <t>-19,45; 28,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 24,16</t>
+          <t>-39,75; 31,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 38,69</t>
+          <t>-9,46; 36,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 13,59</t>
+          <t>-29,03; 10,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 12,08</t>
+          <t>-42,68; 9,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 41,28</t>
+          <t>4,82; 39,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 14,03</t>
+          <t>-17,29; 13,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 8,63</t>
+          <t>-35,09; 7,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,4</t>
+          <t>-0,61; 8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 1,92</t>
+          <t>-6,58; 2,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 11,59</t>
+          <t>-0,89; 11,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,2</t>
+          <t>-8,18; 0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,25</t>
+          <t>-0,66; 8,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 4,8</t>
+          <t>-8,68; 4,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,06</t>
+          <t>-3,16; 2,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,66</t>
+          <t>-2,79; 3,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 5,86</t>
+          <t>-4,36; 5,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 44,73</t>
+          <t>-3,14; 41,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 10,06</t>
+          <t>-28,73; 10,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 58,03</t>
+          <t>-6,06; 58,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 0,51</t>
+          <t>-39,58; 2,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 50,12</t>
+          <t>-3,76; 50,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 28,99</t>
+          <t>-42,24; 24,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 16,71</t>
+          <t>-14,65; 16,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 19,85</t>
+          <t>-13,11; 17,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 30,59</t>
+          <t>-20,74; 30,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,0</t>
+          <t>-2,63; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,04</t>
+          <t>-6,18; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,62</t>
+          <t>1,29; 10,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 7,77</t>
+          <t>-0,07; 7,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,19</t>
+          <t>-1,78; 5,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,74</t>
+          <t>0,63; 7,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,42</t>
+          <t>0,03; 5,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,36</t>
+          <t>-2,7; 2,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,43</t>
+          <t>2,44; 8,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 47,98</t>
+          <t>-15,76; 47,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 9,34</t>
+          <t>-36,98; 11,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 82,55</t>
+          <t>7,13; 84,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 75,7</t>
+          <t>0,81; 81,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 52,59</t>
+          <t>-13,55; 55,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 79,12</t>
+          <t>4,45; 81,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 46,83</t>
+          <t>-0,57; 45,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 19,77</t>
+          <t>-19,38; 22,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 71,35</t>
+          <t>16,57; 69,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,01</t>
+          <t>-3,7; 5,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 0,39</t>
+          <t>-7,88; 0,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 0,91</t>
+          <t>-12,58; 1,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,59</t>
+          <t>-1,91; 5,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 5,09</t>
+          <t>-1,97; 5,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,9</t>
+          <t>-0,17; 6,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,9</t>
+          <t>-1,88; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,77</t>
+          <t>-4,33; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,58</t>
+          <t>-6,36; 2,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 37,77</t>
+          <t>-20,6; 37,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 2,45</t>
+          <t>-43,54; -0,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 4,91</t>
+          <t>-67,87; 7,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 70,88</t>
+          <t>-17,22; 70,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 65,25</t>
+          <t>-17,22; 66,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 90,52</t>
+          <t>-1,32; 86,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 33,34</t>
+          <t>-13,03; 36,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 15,61</t>
+          <t>-29,68; 14,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 20,54</t>
+          <t>-45,58; 21,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,09</t>
+          <t>-3,56; 4,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,05</t>
+          <t>-3,29; 5,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>-0,34; 7,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,33</t>
+          <t>-1,68; 5,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 7,58</t>
+          <t>-0,34; 7,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,89</t>
+          <t>1,46; 7,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,09</t>
+          <t>-1,53; 4,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,05</t>
+          <t>-0,45; 4,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,82</t>
+          <t>1,63; 6,78</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 54,52</t>
+          <t>-31,29; 64,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 70,44</t>
+          <t>-27,64; 71,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 103,54</t>
+          <t>-3,29; 97,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 119,55</t>
+          <t>-19,64; 111,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 146,09</t>
+          <t>-7,6; 138,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,19; 149,03</t>
+          <t>14,33; 143,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 56,96</t>
+          <t>-16,78; 60,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 71,58</t>
+          <t>-4,62; 70,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,56; 98,3</t>
+          <t>16,65; 100,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,71</t>
+          <t>-2,12; 5,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,24</t>
+          <t>-2,75; 4,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 7,29</t>
+          <t>-0,1; 7,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,94</t>
+          <t>-1,55; 5,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,42; 7,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,77</t>
+          <t>-3,97; 3,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,22</t>
+          <t>-0,73; 4,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,95</t>
+          <t>-0,22; 5,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,17</t>
+          <t>-2,71; 4,1</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 165,87</t>
+          <t>-32,16; 159,72</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 151,77</t>
+          <t>-40,64; 128,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 201,29</t>
+          <t>-3,21; 216,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 171,89</t>
+          <t>-30,17; 172,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 243,71</t>
+          <t>-0,88; 232,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 108,86</t>
+          <t>-64,76; 105,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 115,96</t>
+          <t>-12,44; 121,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 137,79</t>
+          <t>-4,32; 150,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 107,3</t>
+          <t>-39,34; 101,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,22</t>
+          <t>-6,76; 0,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,93</t>
+          <t>-5,4; 3,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,62</t>
+          <t>-2,84; 5,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,95</t>
+          <t>0,95; 6,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,87</t>
+          <t>-0,0; 5,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,01</t>
+          <t>1,33; 5,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,9</t>
+          <t>-1,41; 3,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,15</t>
+          <t>-1,36; 3,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,62</t>
+          <t>0,71; 4,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,98; 56,34</t>
+          <t>-83,28; 39,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 91,78</t>
+          <t>-65,48; 91,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 178,98</t>
+          <t>-33,25; 148,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1136,52</t>
+          <t>17,9; 1188,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 997,69</t>
+          <t>-16,5; 891,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,11; 1261,98</t>
+          <t>29,83; 1346,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 146,34</t>
+          <t>-33,12; 155,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 156,33</t>
+          <t>-33,65; 171,33</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,96; 251,18</t>
+          <t>12,62; 239,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,82</t>
+          <t>0,05; 3,55</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,44</t>
+          <t>-4,13; -0,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,07</t>
+          <t>-3,68; 2,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,72</t>
+          <t>-0,62; 2,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,78</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,59</t>
+          <t>-2,82; 1,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,66</t>
+          <t>0,3; 2,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,76</t>
+          <t>-1,69; 0,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,24</t>
+          <t>-2,23; 1,28</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,47; 25,95</t>
+          <t>0,36; 23,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -2,96</t>
+          <t>-24,68; -3,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 13,83</t>
+          <t>-22,86; 13,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 23,21</t>
+          <t>-4,9; 22,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 23,87</t>
+          <t>-4,8; 22,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 13,29</t>
+          <t>-21,58; 14,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,31; 19,87</t>
+          <t>2,17; 20,01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 5,63</t>
+          <t>-11,48; 5,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 9,04</t>
+          <t>-15,6; 9,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,11</t>
+          <t>-5,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,07</t>
+          <t>-4,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 13,54</t>
+          <t>2,66; 13,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,04</t>
+          <t>-4,91; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 6,51</t>
+          <t>-9,53; 5,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 8,84</t>
+          <t>-1,99; 9,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,58</t>
+          <t>-8,81; 3,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 2,01</t>
+          <t>-12,46; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,36</t>
+          <t>1,34; 9,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,15</t>
+          <t>-5,27; 3,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 1,82</t>
+          <t>-9,68; 0,87</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-12,52%</t>
+          <t>-9,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,85%</t>
+          <t>-22,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,02%</t>
+          <t>-15,97%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 63,67</t>
+          <t>10,19; 64,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 28,12</t>
+          <t>-18,94; 29,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 31,02</t>
+          <t>-37,06; 24,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 36,29</t>
+          <t>-6,81; 40,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 10,72</t>
+          <t>-29,5; 12,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 9,26</t>
+          <t>-42,9; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 39,32</t>
+          <t>5,42; 43,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 13,73</t>
+          <t>-19,19; 13,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 7,75</t>
+          <t>-36,62; 3,44</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 8,18</t>
+          <t>-1,35; 7,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,04</t>
+          <t>-6,89; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,46</t>
+          <t>-0,45; 12,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,3</t>
+          <t>-8,53; 0,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 8,48</t>
+          <t>-1,1; 8,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 4,36</t>
+          <t>-4,42; 6,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,98</t>
+          <t>-2,81; 3,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,32</t>
+          <t>-2,7; 3,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,83</t>
+          <t>-0,65; 7,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 41,8</t>
+          <t>-6,0; 40,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 10,48</t>
+          <t>-28,79; 10,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 58,11</t>
+          <t>-1,71; 66,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 2,41</t>
+          <t>-40,03; 4,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 50,59</t>
+          <t>-5,71; 51,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 24,77</t>
+          <t>-21,36; 37,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 16,09</t>
+          <t>-13,47; 19,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 17,88</t>
+          <t>-12,6; 21,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 30,99</t>
+          <t>-3,9; 39,31</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,07</t>
+          <t>-2,76; 5,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,38</t>
+          <t>-6,35; 1,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,97</t>
+          <t>1,81; 10,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,83</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,47</t>
+          <t>-1,61; 5,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,97</t>
+          <t>0,72; 7,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,5</t>
+          <t>0,09; 5,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,55</t>
+          <t>-2,73; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,16</t>
+          <t>2,22; 7,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 47,14</t>
+          <t>-16,03; 45,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 11,15</t>
+          <t>-38,21; 10,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,13; 84,72</t>
+          <t>11,13; 87,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 81,97</t>
+          <t>-2,12; 77,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 55,92</t>
+          <t>-11,83; 56,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 81,29</t>
+          <t>5,05; 81,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 45,8</t>
+          <t>0,59; 49,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 22,16</t>
+          <t>-18,87; 18,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,57; 69,22</t>
+          <t>15,74; 68,86</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>1,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,14</t>
+          <t>-4,0; 4,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,01</t>
+          <t>-8,42; 0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 1,06</t>
+          <t>-4,92; 4,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,63</t>
+          <t>-2,06; 5,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,29</t>
+          <t>-2,53; 4,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 6,87</t>
+          <t>0,72; 7,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,07</t>
+          <t>-1,76; 3,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,63</t>
+          <t>-3,91; 1,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,62</t>
+          <t>-0,92; 4,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-1,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-6,57%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 37,72</t>
+          <t>-21,26; 36,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,54; -0,15</t>
+          <t>-45,21; 1,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 7,72</t>
+          <t>-26,04; 30,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 70,35</t>
+          <t>-18,27; 64,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 66,42</t>
+          <t>-21,57; 60,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 86,3</t>
+          <t>5,21; 95,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 36,9</t>
+          <t>-12,74; 33,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 14,12</t>
+          <t>-27,75; 14,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 21,8</t>
+          <t>-5,78; 40,61</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,76</t>
+          <t>-3,74; 4,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,24</t>
+          <t>-3,14; 5,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,39</t>
+          <t>-0,47; 7,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,95</t>
+          <t>-1,35; 5,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,26</t>
+          <t>-0,11; 7,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,7</t>
+          <t>1,41; 7,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,25</t>
+          <t>-1,33; 4,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,96</t>
+          <t>-0,43; 5,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,78</t>
+          <t>1,74; 6,95</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 64,65</t>
+          <t>-32,17; 57,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 71,97</t>
+          <t>-27,93; 66,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 97,48</t>
+          <t>-4,29; 99,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 111,44</t>
+          <t>-16,54; 114,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 138,55</t>
+          <t>-2,11; 146,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,33; 143,39</t>
+          <t>15,18; 159,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 60,39</t>
+          <t>-14,19; 62,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 70,46</t>
+          <t>-5,53; 78,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,65; 100,82</t>
+          <t>16,96; 104,43</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>3,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,64</t>
+          <t>-1,84; 6,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,75</t>
+          <t>-2,72; 4,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 7,1</t>
+          <t>0,77; 8,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,01</t>
+          <t>-1,55; 4,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,48</t>
+          <t>0,28; 7,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,7</t>
+          <t>-0,1; 5,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,35</t>
+          <t>-0,93; 4,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,12</t>
+          <t>-0,34; 5,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,1</t>
+          <t>1,33; 5,99</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 159,72</t>
+          <t>-28,4; 167,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 128,88</t>
+          <t>-42,35; 137,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 216,35</t>
+          <t>7,78; 234,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 172,85</t>
+          <t>-30,4; 175,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 232,29</t>
+          <t>3,77; 272,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 105,73</t>
+          <t>-3,3; 190,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 121,17</t>
+          <t>-17,61; 124,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 150,13</t>
+          <t>-6,12; 154,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 101,67</t>
+          <t>21,16; 174,46</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 0,88</t>
+          <t>-6,44; 1,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,02</t>
+          <t>-5,43; 3,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,26</t>
+          <t>-2,49; 5,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,05</t>
+          <t>0,83; 5,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,19</t>
+          <t>-0,13; 4,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,13</t>
+          <t>1,4; 5,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,15</t>
+          <t>-1,25; 3,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,35</t>
+          <t>-1,41; 3,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,79</t>
+          <t>0,76; 4,55</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>240,46%</t>
+          <t>238,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 39,89</t>
+          <t>-81,82; 46,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 91,96</t>
+          <t>-67,61; 103,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 148,86</t>
+          <t>-33,23; 170,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,9; 1188,6</t>
+          <t>14,17; 1267,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 891,87</t>
+          <t>-23,05; 1031,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,83; 1346,66</t>
+          <t>35,03; 1286,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 155,65</t>
+          <t>-30,94; 148,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 171,33</t>
+          <t>-36,73; 166,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12,62; 239,97</t>
+          <t>14,87; 233,37</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,55</t>
+          <t>0,05; 3,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,51</t>
+          <t>-4,09; -0,47</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,04</t>
+          <t>-0,76; 3,23</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,69</t>
+          <t>-0,43; 2,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,7</t>
+          <t>-0,56; 2,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,64</t>
+          <t>-0,43; 2,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,69</t>
+          <t>0,19; 2,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,71</t>
+          <t>-1,72; 0,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,28</t>
+          <t>-0,18; 2,35</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-1,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-0,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,36; 23,88</t>
+          <t>0,29; 24,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,68; -3,25</t>
+          <t>-24,28; -3,17</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 13,27</t>
+          <t>-4,45; 21,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 22,97</t>
+          <t>-3,31; 21,82</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 22,52</t>
+          <t>-4,13; 22,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 14,04</t>
+          <t>-3,14; 21,07</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,17; 20,01</t>
+          <t>1,27; 19,59</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 5,31</t>
+          <t>-11,87; 4,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 9,34</t>
+          <t>-1,32; 17,15</t>
         </is>
       </c>
     </row>
